--- a/data/trans_orig/IP31KM06_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM06_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7678</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4747</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11535</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7346</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4081</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11923</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,64%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16096</t>
+          <t>14871</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29757</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25900</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32688</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>69,19%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>39149</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>34572</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>42414</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>84,2%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74,36%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36535</t>
+          <t>35488</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31858</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40085</t>
+          <t>38469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>75683</t>
+          <t>65245</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69352</t>
+          <t>59588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80629</t>
+          <t>69830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53313</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43656</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>62678</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>38134</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>28900</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>46566</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>23,94%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60749</t>
+          <t>37204</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50671</t>
+          <t>29214</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72208</t>
+          <t>45893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>98883</t>
+          <t>90518</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85733</t>
+          <t>78048</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114115</t>
+          <t>103234</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>103729</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>94364</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>113386</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>60,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>72,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>121165</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>112733</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>130399</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>76,06%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>121210</t>
+          <t>108314</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109751</t>
+          <t>99625</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>131288</t>
+          <t>116304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>242376</t>
+          <t>212042</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>227144</t>
+          <t>199326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255526</t>
+          <t>224512</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>67633</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55122</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>82059</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,54%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>62579</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>51113</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73922</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>36,16%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>42,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73102</t>
+          <t>63318</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59611</t>
+          <t>53180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87419</t>
+          <t>75336</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>135681</t>
+          <t>130952</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119776</t>
+          <t>115666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155198</t>
+          <t>146949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>132493</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>118067</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145004</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>66,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>59,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,46%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>110493</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>99150</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>121959</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>63,84%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,47%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>139388</t>
+          <t>111354</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125071</t>
+          <t>99336</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152879</t>
+          <t>121492</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>249882</t>
+          <t>243846</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230365</t>
+          <t>227849</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>265787</t>
+          <t>259132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>136557</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>117706</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>157816</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>46,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>40,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>54,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>122071</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>99995</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>169148</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>44,51%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>61,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>141733</t>
+          <t>103487</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122487</t>
+          <t>90658</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167543</t>
+          <t>117806</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>263804</t>
+          <t>240044</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233685</t>
+          <t>216956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>318621</t>
+          <t>264698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>155664</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>134405</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>174515</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>59,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>152196</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>105119</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>174272</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>55,49%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>38,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>163266</t>
+          <t>151850</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137456</t>
+          <t>137531</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>182512</t>
+          <t>164679</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>315462</t>
+          <t>307514</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260645</t>
+          <t>282860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>345581</t>
+          <t>330602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,38%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>265182</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>241225</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>291196</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>42,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>290</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>230130</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>202004</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>287541</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>35,23%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>44,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>284334</t>
+          <t>211202</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>254866</t>
+          <t>191598</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>315021</t>
+          <t>234513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>514464</t>
+          <t>476384</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>479166</t>
+          <t>444019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>575961</t>
+          <t>512656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>421642</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>395628</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>445599</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>61,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>57,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>64,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>423004</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>365593</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>451130</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>64,77%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>55,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>69,07%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>460399</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>429712</t>
+          <t>383695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489867</t>
+          <t>426610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>883403</t>
+          <t>828647</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>821906</t>
+          <t>792375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>918701</t>
+          <t>861012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
